--- a/docs/stage-20260908/A/evidence/inventory-selected.xlsx
+++ b/docs/stage-20260908/A/evidence/inventory-selected.xlsx
@@ -103,7 +103,7 @@
     <t>LOT-1</t>
   </si>
   <si>
-    <t>cmts782o80000xpostk523yrg</t>
+    <t>cmts9bm7e0000ewosy6lqdhcy</t>
   </si>
   <si>
     <t>precise</t>
